--- a/artfynd/A 72173-2021 artfynd.xlsx
+++ b/artfynd/A 72173-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72173-2021 artfynd.xlsx
+++ b/artfynd/A 72173-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110941011</v>
+        <v>110941092</v>
       </c>
       <c r="B2" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548652.4368706662</v>
+        <v>548876</v>
       </c>
       <c r="R2" t="n">
-        <v>7263755.479863233</v>
+        <v>7263786</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110941092</v>
+        <v>110940966</v>
       </c>
       <c r="B3" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548876.0892321788</v>
+        <v>548873</v>
       </c>
       <c r="R3" t="n">
-        <v>7263785.391704368</v>
+        <v>7263784</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110940988</v>
+        <v>110941010</v>
       </c>
       <c r="B4" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548656.5944080142</v>
+        <v>548718</v>
       </c>
       <c r="R4" t="n">
-        <v>7263755.549276625</v>
+        <v>7263741</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110941136</v>
+        <v>110941011</v>
       </c>
       <c r="B5" t="n">
-        <v>96350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548801.4837844274</v>
+        <v>548653</v>
       </c>
       <c r="R5" t="n">
-        <v>7263770.433649954</v>
+        <v>7263755</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110940994</v>
+        <v>110941137</v>
       </c>
       <c r="B6" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548893.8340823351</v>
+        <v>548839</v>
       </c>
       <c r="R6" t="n">
-        <v>7263793.581677854</v>
+        <v>7263787</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110941137</v>
+        <v>110941118</v>
       </c>
       <c r="B7" t="n">
-        <v>89793</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548839.0527181671</v>
+        <v>548832</v>
       </c>
       <c r="R7" t="n">
-        <v>7263786.847685082</v>
+        <v>7263785</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110941093</v>
+        <v>110941119</v>
       </c>
       <c r="B8" t="n">
-        <v>97322</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222467</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548788.4647774538</v>
+        <v>548753</v>
       </c>
       <c r="R8" t="n">
-        <v>7263753.184761007</v>
+        <v>7263745</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110941010</v>
+        <v>110940988</v>
       </c>
       <c r="B9" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548717.5513079804</v>
+        <v>548657</v>
       </c>
       <c r="R9" t="n">
-        <v>7263741.198281654</v>
+        <v>7263755</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110941118</v>
+        <v>110941135</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548832.0197720311</v>
+        <v>548945</v>
       </c>
       <c r="R10" t="n">
-        <v>7263784.652903262</v>
+        <v>7263599</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>06:17</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>06:17</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110941119</v>
+        <v>110941136</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548752.8419177117</v>
+        <v>548801</v>
       </c>
       <c r="R11" t="n">
-        <v>7263744.696191267</v>
+        <v>7263770</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110941106</v>
+        <v>110940994</v>
       </c>
       <c r="B12" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548973.0045342735</v>
+        <v>548894</v>
       </c>
       <c r="R12" t="n">
-        <v>7263635.814689283</v>
+        <v>7263793</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110940966</v>
+        <v>110940995</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548873.1929140337</v>
+        <v>548736</v>
       </c>
       <c r="R13" t="n">
-        <v>7263784.512358888</v>
+        <v>7263749</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110940995</v>
+        <v>110941093</v>
       </c>
       <c r="B14" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548736.558009455</v>
+        <v>548789</v>
       </c>
       <c r="R14" t="n">
-        <v>7263748.577712097</v>
+        <v>7263753</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
